--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{3C6B5F0E-19AD-46E6-BF2E-01B31D2048A5}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{4A753B77-D850-4D4A-BA08-4D6E3FD0B859}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Edition" sheetId="2" r:id="rId2"/>
+    <sheet name="Paid Details" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -62,6 +63,21 @@
   </si>
   <si>
     <t>Checked</t>
+  </si>
+  <si>
+    <t>CheckNumber__c</t>
+  </si>
+  <si>
+    <t>VoucherNumber__c</t>
+  </si>
+  <si>
+    <t>PaidDate__c</t>
+  </si>
+  <si>
+    <t>PaymentReference__c</t>
+  </si>
+  <si>
+    <t>Nil</t>
   </si>
 </sst>
 </file>
@@ -510,4 +526,74 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B525EBA-C08E-4BA7-8EAD-8589568CEF96}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>6789678654</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>5678</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{4A753B77-D850-4D4A-BA08-4D6E3FD0B859}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{1BC708E0-49C9-4AB9-83C2-BCFC0F0B3972}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition" sheetId="2" r:id="rId2"/>
-    <sheet name="Paid Details" sheetId="3" r:id="rId3"/>
+    <sheet name="Advance Edition" sheetId="4" r:id="rId2"/>
+    <sheet name="Edition" sheetId="2" r:id="rId3"/>
+    <sheet name="Paid Details" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -78,6 +79,9 @@
   </si>
   <si>
     <t>Nil</t>
+  </si>
+  <si>
+    <t>Overview</t>
   </si>
 </sst>
 </file>
@@ -470,6 +474,76 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A3052A-53B6-4404-9922-9D5C64B8A322}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>78954</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC07F6C2-F9EE-4A78-8EFB-9F3B27056F73}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -528,7 +602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B525EBA-C08E-4BA7-8EAD-8589568CEF96}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:100000_{1BC708E0-49C9-4AB9-83C2-BCFC0F0B3972}" xr6:coauthVersionLast="31" xr6:coauthVersionMax="31" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1F4B82-2355-48D1-A9D4-38388B7F6B65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -45,9 +45,6 @@
     <t>Title__c</t>
   </si>
   <si>
-    <t>Automation Payment Request</t>
-  </si>
-  <si>
     <t>YTDEarnedAmount__c</t>
   </si>
   <si>
@@ -82,6 +79,9 @@
   </si>
   <si>
     <t>Overview</t>
+  </si>
+  <si>
+    <t>Automation Payment Request Regression</t>
   </si>
 </sst>
 </file>
@@ -443,7 +443,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -465,7 +465,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -496,10 +496,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>78954</v>
@@ -507,10 +507,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -518,24 +518,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -565,10 +565,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -576,24 +576,24 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -627,7 +627,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>6789678654</v>
@@ -638,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>5678</v>
@@ -649,7 +649,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>-5</v>
@@ -660,10 +660,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1F4B82-2355-48D1-A9D4-38388B7F6B65}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFBAED8-7C78-4A28-9863-37BCC626668E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
     <t>Overview</t>
   </si>
   <si>
-    <t>Automation Payment Request Regression</t>
+    <t xml:space="preserve">Automation Payment Request </t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFBAED8-7C78-4A28-9863-37BCC626668E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCE0D61-E27D-418B-A4E6-21DC32BF7DE9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -440,13 +440,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493C7654-D1A3-4E56-B510-F05D117ABEF1}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -476,14 +476,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A3052A-53B6-4404-9922-9D5C64B8A322}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.21875" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,7 +494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -505,7 +505,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -516,7 +516,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -527,7 +527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -546,13 +546,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC07F6C2-F9EE-4A78-8EFB-9F3B27056F73}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,7 +563,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -574,7 +574,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -585,7 +585,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -605,13 +605,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B525EBA-C08E-4BA7-8EAD-8589568CEF96}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -633,7 +633,7 @@
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -644,7 +644,7 @@
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -655,7 +655,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCE0D61-E27D-418B-A4E6-21DC32BF7DE9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3DB20064-4C88-40D6-9C39-740182FAD6DF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Advance Edition" sheetId="4" r:id="rId2"/>
     <sheet name="Edition" sheetId="2" r:id="rId3"/>
     <sheet name="Paid Details" sheetId="3" r:id="rId4"/>
+    <sheet name="No Program Income_Edition" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="179017"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -87,8 +82,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,7 +180,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -237,7 +232,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -431,22 +426,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493C7654-D1A3-4E56-B510-F05D117ABEF1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -474,16 +469,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A3052A-53B6-4404-9922-9D5C64B8A322}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -494,7 +489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -505,7 +500,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -516,7 +511,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -527,7 +522,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -544,15 +539,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC07F6C2-F9EE-4A78-8EFB-9F3B27056F73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,7 +558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -574,7 +569,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -585,7 +580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -603,15 +598,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B525EBA-C08E-4BA7-8EAD-8589568CEF96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -633,7 +628,7 @@
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -644,7 +639,7 @@
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -655,7 +650,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -670,4 +665,51 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FB4B2D-6B3B-4CCC-AFB4-025AE7818F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -14,8 +20,8 @@
     <sheet name="No Program Income_Edition" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -82,8 +88,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,22 +432,22 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -469,16 +475,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,7 +495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -500,7 +506,7 @@
         <v>78954</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -511,7 +517,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -522,7 +528,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -539,15 +545,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -569,7 +575,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -580,7 +586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -598,15 +604,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,7 +623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -628,7 +634,7 @@
         <v>6789678654</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -639,7 +645,7 @@
         <v>5678</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -650,7 +656,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -668,15 +674,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,7 +693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -698,7 +704,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/src/main/resources/PaymentRequest_Field_Values.xlsx
+++ b/src/main/resources/PaymentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_New_Clone\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5FB4B2D-6B3B-4CCC-AFB4-025AE7818F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB51AE2E-4E15-4AB1-A932-275CAA85AC51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Adhoc Reimbursement Creation" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Edition" sheetId="2" r:id="rId3"/>
     <sheet name="Paid Details" sheetId="3" r:id="rId4"/>
     <sheet name="No Program Income_Edition" sheetId="5" r:id="rId5"/>
+    <sheet name="SF270_Form" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="79">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -83,19 +84,208 @@
   </si>
   <si>
     <t xml:space="preserve">Automation Payment Request </t>
+  </si>
+  <si>
+    <t>fieldTypeOfRequest__c</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>fieldBasisOfRequest__c</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>fieldFederalAgencySF428__c</t>
+  </si>
+  <si>
+    <t>TEST12345</t>
+  </si>
+  <si>
+    <t>fieldFederalAwardIdentifier__c</t>
+  </si>
+  <si>
+    <t>fieldPartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>fieldFinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>fieldPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldRecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
+    <t>TEST Organization</t>
+  </si>
+  <si>
+    <t>fieldStreet1SF428__c</t>
+  </si>
+  <si>
+    <t>fieldStreet2SF428__c</t>
+  </si>
+  <si>
+    <t>Street 2</t>
+  </si>
+  <si>
+    <t>fieldCitySF428__c</t>
+  </si>
+  <si>
+    <t>fieldCountySF428__c</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>fieldStateSf428__c</t>
+  </si>
+  <si>
+    <t>fieldProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>fieldCountrySF428__c</t>
+  </si>
+  <si>
+    <t>USA: UNITED STATES</t>
+  </si>
+  <si>
+    <t>fieldZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCity__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCounty__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeState__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeProvince__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCountry__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>fieldPrograms__c</t>
+  </si>
+  <si>
+    <t>fieldFunctions__c</t>
+  </si>
+  <si>
+    <t>fieldActivities__c</t>
+  </si>
+  <si>
+    <t>fieldAcquiredDate__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedFederalCashOutlays__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedBalanceofFederalCashonHand__c</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgementSF428__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>fieldSubmittedBySF428__c</t>
+  </si>
+  <si>
+    <t>John Mathews</t>
+  </si>
+  <si>
+    <t>fieldSubmittedOn__c</t>
+  </si>
+  <si>
+    <t>fieldPrefix__c</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>fieldFirstNameSF428__c</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>fieldMiddleNameSF428__c</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>fieldLastNameSF428__c</t>
+  </si>
+  <si>
+    <t>Mathews</t>
+  </si>
+  <si>
+    <t>fieldSuffix__c</t>
+  </si>
+  <si>
+    <t>Jr.</t>
+  </si>
+  <si>
+    <t>fieldTitleSF429__c</t>
+  </si>
+  <si>
+    <t>Associate</t>
+  </si>
+  <si>
+    <t>fieldTelephone__c</t>
+  </si>
+  <si>
+    <t>fieldAgencyCommentsSF428__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>12345-1234</t>
+  </si>
+  <si>
+    <t>NY: New York</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -118,13 +308,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -186,7 +382,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -238,7 +434,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -680,6 +876,7 @@
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -718,4 +915,503 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20A769E-7CDB-4643-B4E8-C9AF9D26E6C8}">
+  <dimension ref="A1:C44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3">
+        <v>123456789</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2121323223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2121323223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="3">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="3">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="3">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>